--- a/رسم ترم ثاني.xlsx
+++ b/رسم ترم ثاني.xlsx
@@ -442,19 +442,19 @@
         <v>مستجد</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G2">
         <v>13</v>
       </c>
       <c r="H2">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J2">
         <v>118</v>
       </c>
       <c r="K2">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
@@ -474,19 +474,19 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G3">
         <v>8</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J3">
         <v>100</v>
       </c>
       <c r="K3">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
@@ -506,19 +506,19 @@
         <v>مستجد</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G4">
         <v>13</v>
       </c>
       <c r="H4">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J4">
         <v>134</v>
       </c>
       <c r="K4">
-        <v>163</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5">
@@ -570,19 +570,19 @@
         <v>مستجد</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G6">
         <v>13</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J6">
         <v>108</v>
       </c>
       <c r="K6">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7">
@@ -602,19 +602,19 @@
         <v>مستجد</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G7">
         <v>7</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J7">
         <v>123</v>
       </c>
       <c r="K7">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8">
@@ -730,19 +730,19 @@
         <v>مستجد</v>
       </c>
       <c r="F11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G11">
         <v>13</v>
       </c>
       <c r="H11">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J11">
         <v>133</v>
       </c>
       <c r="K11">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -762,19 +762,19 @@
         <v>مستجد</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>14</v>
       </c>
       <c r="H12">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J12">
         <v>86</v>
       </c>
       <c r="K12">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13">
@@ -826,19 +826,19 @@
         <v>مستجد</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G14">
         <v>22</v>
       </c>
       <c r="H14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J14">
         <v>175</v>
       </c>
       <c r="K14">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15">
@@ -890,19 +890,19 @@
         <v>مستجد</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>12</v>
       </c>
       <c r="H16">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J16">
         <v>77</v>
       </c>
       <c r="K16">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
@@ -922,19 +922,19 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G17">
         <v>14</v>
       </c>
       <c r="H17">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J17">
         <v>122</v>
       </c>
       <c r="K17">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
@@ -954,19 +954,19 @@
         <v>مستجد</v>
       </c>
       <c r="F18">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G18" t="str">
         <v>غ</v>
       </c>
       <c r="H18">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J18">
         <v>128</v>
       </c>
       <c r="K18">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19">
@@ -986,19 +986,19 @@
         <v>مستجد</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G19">
         <v>4</v>
       </c>
       <c r="H19">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J19">
         <v>68</v>
       </c>
       <c r="K19">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20">
@@ -1018,19 +1018,19 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G20">
         <v>21</v>
       </c>
       <c r="H20">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J20">
         <v>185</v>
       </c>
       <c r="K20">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21">
@@ -1050,19 +1050,19 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G21">
         <v>12</v>
       </c>
       <c r="H21">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22">
@@ -1082,19 +1082,19 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G22">
         <v>12</v>
       </c>
       <c r="H22">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J22">
         <v>97</v>
       </c>
       <c r="K22">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23">
@@ -1114,19 +1114,19 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G23">
         <v>18</v>
       </c>
       <c r="H23">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J23">
         <v>94</v>
       </c>
       <c r="K23">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24">
@@ -1210,19 +1210,19 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G26">
         <v>14</v>
       </c>
       <c r="H26">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J26">
         <v>105</v>
       </c>
       <c r="K26">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27">
@@ -1242,19 +1242,19 @@
         <v>مستجد</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G27">
         <v>12</v>
       </c>
       <c r="H27">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J27">
         <v>118</v>
       </c>
       <c r="K27">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28">
@@ -1274,19 +1274,19 @@
         <v>مستجد</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G28">
         <v>6</v>
       </c>
       <c r="H28">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J28">
         <v>87</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29">
@@ -1306,19 +1306,19 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G29">
         <v>2</v>
       </c>
       <c r="H29">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J29">
         <v>133</v>
       </c>
       <c r="K29">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30">
@@ -1338,19 +1338,19 @@
         <v>مستجد</v>
       </c>
       <c r="F30">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J30">
         <v>84</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31">
@@ -1370,19 +1370,19 @@
         <v>مستجد</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G31">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J31">
         <v>112</v>
       </c>
       <c r="K31">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1454,19 +1454,19 @@
         <v>مستجد</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G2">
         <v>14</v>
       </c>
       <c r="H2">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J2">
         <v>115</v>
       </c>
       <c r="K2">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
@@ -1486,19 +1486,19 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <v>23</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J3">
         <v>174</v>
       </c>
       <c r="K3">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4">
@@ -1518,19 +1518,19 @@
         <v>مستجد</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J4">
         <v>17</v>
       </c>
       <c r="K4">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -1550,19 +1550,19 @@
         <v>مستجد</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G5">
         <v>21</v>
       </c>
       <c r="H5">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J5">
         <v>152</v>
       </c>
       <c r="K5">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6">
@@ -1614,19 +1614,19 @@
         <v>مستجد</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>14</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J7">
         <v>134</v>
       </c>
       <c r="K7">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
@@ -1646,19 +1646,19 @@
         <v>مستجد</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G8">
         <v>19</v>
       </c>
       <c r="H8">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J8">
         <v>178</v>
       </c>
       <c r="K8">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9">
@@ -1678,19 +1678,19 @@
         <v>مستجد</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <v>11</v>
       </c>
       <c r="H9">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J9">
         <v>102</v>
       </c>
       <c r="K9">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
@@ -1710,19 +1710,19 @@
         <v>مستجد</v>
       </c>
       <c r="F10">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G10">
         <v>18</v>
       </c>
       <c r="H10">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J10">
         <v>146</v>
       </c>
       <c r="K10">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -1806,19 +1806,19 @@
         <v>مستجد</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G13">
         <v>11</v>
       </c>
       <c r="H13">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J13">
         <v>99</v>
       </c>
       <c r="K13">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1838,19 +1838,19 @@
         <v>مستجد</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G14">
         <v>18</v>
       </c>
       <c r="H14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J14">
         <v>159</v>
       </c>
       <c r="K14">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15">
@@ -1870,19 +1870,19 @@
         <v>مستجد</v>
       </c>
       <c r="F15">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J15">
         <v>45</v>
       </c>
       <c r="K15">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1902,19 +1902,19 @@
         <v>مستجد</v>
       </c>
       <c r="F16">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G16">
         <v>15</v>
       </c>
       <c r="H16">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J16">
         <v>127</v>
       </c>
       <c r="K16">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17">
@@ -1934,19 +1934,19 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G17">
         <v>23</v>
       </c>
       <c r="H17">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J17">
         <v>142</v>
       </c>
       <c r="K17">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18">
@@ -1998,19 +1998,19 @@
         <v>مستجد</v>
       </c>
       <c r="F19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19">
         <v>20</v>
       </c>
       <c r="H19">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J19">
         <v>180</v>
       </c>
       <c r="K19">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20">
@@ -2030,19 +2030,19 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G20">
         <v>20</v>
       </c>
       <c r="H20">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J20">
         <v>178</v>
       </c>
       <c r="K20">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21">
@@ -2062,19 +2062,19 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G21">
         <v>9</v>
       </c>
       <c r="H21">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J21">
         <v>94</v>
       </c>
       <c r="K21">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22">
@@ -2094,19 +2094,19 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G22">
         <v>9</v>
       </c>
       <c r="H22">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J22">
         <v>112</v>
       </c>
       <c r="K22">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23">
@@ -2126,19 +2126,19 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G23" t="str">
         <v>غ</v>
       </c>
       <c r="H23">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J23">
         <v>62</v>
       </c>
       <c r="K23">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24">
@@ -2158,19 +2158,19 @@
         <v>مستجد</v>
       </c>
       <c r="F24">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G24">
         <v>24</v>
       </c>
       <c r="H24">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J24">
         <v>173</v>
       </c>
       <c r="K24">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25">
@@ -2222,19 +2222,19 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G26">
         <v>9</v>
       </c>
       <c r="H26">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J26">
         <v>119</v>
       </c>
       <c r="K26">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27">
@@ -2286,19 +2286,19 @@
         <v>مستجد</v>
       </c>
       <c r="F28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G28">
         <v>19</v>
       </c>
       <c r="H28">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J28">
         <v>151</v>
       </c>
       <c r="K28">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29">
@@ -2318,19 +2318,19 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G29">
         <v>16</v>
       </c>
       <c r="H29">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J29">
         <v>149</v>
       </c>
       <c r="K29">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30">
@@ -2382,19 +2382,19 @@
         <v>مستجد</v>
       </c>
       <c r="F31">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G31">
         <v>18</v>
       </c>
       <c r="H31">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J31">
         <v>119</v>
       </c>
       <c r="K31">
-        <v>149</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2466,19 +2466,19 @@
         <v>مستجد</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G2">
         <v>22</v>
       </c>
       <c r="H2">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J2">
         <v>152</v>
       </c>
       <c r="K2">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3">
@@ -2498,19 +2498,19 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <v>14</v>
       </c>
       <c r="H3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J3">
         <v>123</v>
       </c>
       <c r="K3">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4">
@@ -2530,19 +2530,19 @@
         <v>مستجد</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G4">
         <v>9</v>
       </c>
       <c r="H4">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J4">
         <v>82</v>
       </c>
       <c r="K4">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5">
@@ -2562,19 +2562,19 @@
         <v>مستجد</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J5">
         <v>85</v>
       </c>
       <c r="K5">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -2626,19 +2626,19 @@
         <v>مستجد</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G7">
         <v>12</v>
       </c>
       <c r="H7">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J7">
         <v>127</v>
       </c>
       <c r="K7">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8">
@@ -2658,19 +2658,19 @@
         <v>مستجد</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G8">
         <v>22</v>
       </c>
       <c r="H8">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J8">
         <v>182</v>
       </c>
       <c r="K8">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
@@ -2690,19 +2690,19 @@
         <v>مستجد</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G9">
         <v>12</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J9">
         <v>85</v>
       </c>
       <c r="K9">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
@@ -2722,19 +2722,19 @@
         <v>مستجد</v>
       </c>
       <c r="F10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G10">
         <v>15</v>
       </c>
       <c r="H10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J10">
         <v>116</v>
       </c>
       <c r="K10">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -2754,19 +2754,19 @@
         <v>مستجد</v>
       </c>
       <c r="F11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G11">
         <v>19</v>
       </c>
       <c r="H11">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J11">
         <v>148</v>
       </c>
       <c r="K11">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12">
@@ -2786,19 +2786,19 @@
         <v>مستجد</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G12">
         <v>9</v>
       </c>
       <c r="H12">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J12">
         <v>94</v>
       </c>
       <c r="K12">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -2818,19 +2818,19 @@
         <v>مستجد</v>
       </c>
       <c r="F13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G13">
         <v>24</v>
       </c>
       <c r="H13">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J13">
         <v>175</v>
       </c>
       <c r="K13">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14">
@@ -2850,19 +2850,19 @@
         <v>مستجد</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G14">
         <v>17</v>
       </c>
       <c r="H14">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J14">
         <v>135</v>
       </c>
       <c r="K14">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15">
@@ -2882,19 +2882,19 @@
         <v>مستجد</v>
       </c>
       <c r="F15">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G15">
         <v>13</v>
       </c>
       <c r="H15">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J15">
         <v>105</v>
       </c>
       <c r="K15">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16">
@@ -2946,19 +2946,19 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G17">
         <v>24</v>
       </c>
       <c r="H17">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J17">
         <v>153</v>
       </c>
       <c r="K17">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18">
@@ -2978,19 +2978,19 @@
         <v>مستجد</v>
       </c>
       <c r="F18">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G18">
         <v>9</v>
       </c>
       <c r="H18">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J18">
         <v>120</v>
       </c>
       <c r="K18">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19">
@@ -3042,19 +3042,19 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G20">
         <v>9</v>
       </c>
       <c r="H20">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J20">
         <v>113</v>
       </c>
       <c r="K20">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
@@ -3074,19 +3074,19 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G21">
         <v>10</v>
       </c>
       <c r="H21">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J21">
         <v>106</v>
       </c>
       <c r="K21">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22">
@@ -3106,19 +3106,19 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G22">
         <v>15</v>
       </c>
       <c r="H22">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J22">
         <v>116</v>
       </c>
       <c r="K22">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23">
@@ -3138,19 +3138,19 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G23">
         <v>21</v>
       </c>
       <c r="H23">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J23">
         <v>178</v>
       </c>
       <c r="K23">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24">
@@ -3170,19 +3170,19 @@
         <v>مستجد</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G24">
         <v>4</v>
       </c>
       <c r="H24">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J24">
         <v>20</v>
       </c>
       <c r="K24">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
@@ -3202,19 +3202,19 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G25">
         <v>19</v>
       </c>
       <c r="H25">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J25">
         <v>127</v>
       </c>
       <c r="K25">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26">
@@ -3234,19 +3234,19 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G26">
         <v>11</v>
       </c>
       <c r="H26">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J26">
         <v>69</v>
       </c>
       <c r="K26">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27">
@@ -3266,19 +3266,19 @@
         <v>مستجد</v>
       </c>
       <c r="F27">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G27">
         <v>17</v>
       </c>
       <c r="H27">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J27">
         <v>124</v>
       </c>
       <c r="K27">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28">
@@ -3298,19 +3298,19 @@
         <v>مستجد</v>
       </c>
       <c r="F28">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G28">
         <v>19</v>
       </c>
       <c r="H28">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J28">
         <v>103</v>
       </c>
       <c r="K28">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29">
@@ -3330,13 +3330,13 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G29" t="str">
         <v>غ</v>
       </c>
       <c r="H29">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J29" t="str">
         <v>غ</v>
@@ -3362,19 +3362,19 @@
         <v>مستجد</v>
       </c>
       <c r="F30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G30">
         <v>24</v>
       </c>
       <c r="H30">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J30">
         <v>195</v>
       </c>
       <c r="K30">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31">
@@ -3394,19 +3394,19 @@
         <v>مستجد</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G31">
         <v>10</v>
       </c>
       <c r="H31">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J31">
         <v>120</v>
       </c>
       <c r="K31">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -3478,13 +3478,13 @@
         <v>مستجد</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G2" t="str">
         <v>غ</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J2" t="str">
         <v>غ</v>
@@ -3510,19 +3510,19 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <v>78</v>
       </c>
       <c r="K3">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
@@ -3542,19 +3542,19 @@
         <v>مستجد</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G4">
         <v>14</v>
       </c>
       <c r="H4">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J4">
         <v>145</v>
       </c>
       <c r="K4">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
@@ -3606,19 +3606,19 @@
         <v>مستجد</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>10</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J6">
         <v>78</v>
       </c>
       <c r="K6">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7">
@@ -3638,19 +3638,19 @@
         <v>مستجد</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>19</v>
       </c>
       <c r="H7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J7">
         <v>174</v>
       </c>
       <c r="K7">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8">
@@ -3670,19 +3670,19 @@
         <v>مستجد</v>
       </c>
       <c r="F8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G8">
         <v>23</v>
       </c>
       <c r="H8">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J8">
         <v>167</v>
       </c>
       <c r="K8">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9">
@@ -3702,19 +3702,19 @@
         <v>مستجد</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <v>23</v>
       </c>
       <c r="H9">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J9">
         <v>136</v>
       </c>
       <c r="K9">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -3734,19 +3734,19 @@
         <v>مستجد</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G10" t="str">
         <v>غ</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J10">
         <v>118</v>
       </c>
       <c r="K10">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -3766,19 +3766,19 @@
         <v>مستجد</v>
       </c>
       <c r="F11">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G11">
         <v>19</v>
       </c>
       <c r="H11">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J11">
         <v>141</v>
       </c>
       <c r="K11">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -3798,19 +3798,19 @@
         <v>مستجد</v>
       </c>
       <c r="F12">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G12">
         <v>8</v>
       </c>
       <c r="H12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J12">
         <v>111</v>
       </c>
       <c r="K12">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -3830,19 +3830,19 @@
         <v>مستجد</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G13" t="str">
         <v>غ</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J13">
         <v>84</v>
       </c>
       <c r="K13">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -3862,19 +3862,19 @@
         <v>مستجد</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G14">
         <v>7</v>
       </c>
       <c r="H14">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J14">
         <v>91</v>
       </c>
       <c r="K14">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15">
@@ -3894,19 +3894,19 @@
         <v>مستجد</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G15">
         <v>12</v>
       </c>
       <c r="H15">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J15">
         <v>117</v>
       </c>
       <c r="K15">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16">
@@ -3926,19 +3926,19 @@
         <v>مستجد</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G16">
         <v>8</v>
       </c>
       <c r="H16">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J16">
         <v>112</v>
       </c>
       <c r="K16">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17">
@@ -3958,19 +3958,19 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G17">
         <v>14</v>
       </c>
       <c r="H17">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J17">
         <v>142</v>
       </c>
       <c r="K17">
-        <v>169</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18">
@@ -4022,19 +4022,19 @@
         <v>مستجد</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G19">
         <v>11</v>
       </c>
       <c r="H19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J19">
         <v>86</v>
       </c>
       <c r="K19">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20">
@@ -4054,19 +4054,19 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G20">
         <v>3</v>
       </c>
       <c r="H20">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J20">
         <v>60</v>
       </c>
       <c r="K20">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
@@ -4086,19 +4086,19 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G21">
         <v>15</v>
       </c>
       <c r="H21">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J21">
         <v>128</v>
       </c>
       <c r="K21">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22">
@@ -4118,19 +4118,19 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G22">
         <v>22</v>
       </c>
       <c r="H22">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J22">
         <v>160</v>
       </c>
       <c r="K22">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23">
@@ -4150,19 +4150,19 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G23">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J23">
         <v>94</v>
       </c>
       <c r="K23">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
@@ -4182,19 +4182,19 @@
         <v>مستجد</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G24">
         <v>9</v>
       </c>
       <c r="H24">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J24">
         <v>71</v>
       </c>
       <c r="K24">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25">
@@ -4214,19 +4214,19 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G25">
         <v>3</v>
       </c>
       <c r="H25">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J25">
         <v>133</v>
       </c>
       <c r="K25">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26">
@@ -4246,19 +4246,19 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G26">
         <v>9</v>
       </c>
       <c r="H26">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J26">
         <v>97</v>
       </c>
       <c r="K26">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27">
@@ -4278,19 +4278,19 @@
         <v>مستجد</v>
       </c>
       <c r="F27">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G27">
         <v>10</v>
       </c>
       <c r="H27">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J27">
         <v>95</v>
       </c>
       <c r="K27">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28">
@@ -4310,19 +4310,19 @@
         <v>مستجد</v>
       </c>
       <c r="F28">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G28">
         <v>22</v>
       </c>
       <c r="H28">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J28">
         <v>167</v>
       </c>
       <c r="K28">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29">
@@ -4342,19 +4342,19 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G29">
         <v>7</v>
       </c>
       <c r="H29">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J29">
         <v>82</v>
       </c>
       <c r="K29">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30">
@@ -4374,19 +4374,19 @@
         <v>مستجد</v>
       </c>
       <c r="F30">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G30" t="str">
         <v>غ</v>
       </c>
       <c r="H30">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J30">
         <v>128</v>
       </c>
       <c r="K30">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31">
@@ -4406,19 +4406,19 @@
         <v>مستجد</v>
       </c>
       <c r="F31">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G31">
         <v>6</v>
       </c>
       <c r="H31">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J31">
         <v>111</v>
       </c>
       <c r="K31">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -4490,19 +4490,19 @@
         <v>مستجد</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G2">
         <v>11</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J2">
         <v>133</v>
       </c>
       <c r="K2">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
@@ -4522,19 +4522,19 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <v>19</v>
       </c>
       <c r="H3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J3">
         <v>139</v>
       </c>
       <c r="K3">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4">
@@ -4554,19 +4554,19 @@
         <v>مستجد</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G4">
         <v>12</v>
       </c>
       <c r="H4">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J4">
         <v>112</v>
       </c>
       <c r="K4">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5">
@@ -4586,19 +4586,19 @@
         <v>مستجد</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G5">
         <v>23</v>
       </c>
       <c r="H5">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J5">
         <v>163</v>
       </c>
       <c r="K5">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
@@ -4618,19 +4618,19 @@
         <v>مستجد</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G6" t="str">
         <v>غ</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J6">
         <v>126</v>
       </c>
       <c r="K6">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
@@ -4650,19 +4650,19 @@
         <v>مستجد</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>19</v>
       </c>
       <c r="H7">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J7">
         <v>133</v>
       </c>
       <c r="K7">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8">
@@ -4714,19 +4714,19 @@
         <v>مستجد</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <v>17</v>
       </c>
       <c r="H9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J9">
         <v>149</v>
       </c>
       <c r="K9">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -4746,13 +4746,13 @@
         <v>مستجد</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G10">
         <v>8</v>
       </c>
       <c r="H10">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J10" t="str">
         <v>غ</v>
@@ -4778,19 +4778,19 @@
         <v>مستجد</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G11">
         <v>19</v>
       </c>
       <c r="H11">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J11">
         <v>137</v>
       </c>
       <c r="K11">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -4810,19 +4810,19 @@
         <v>مستجد</v>
       </c>
       <c r="F12">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G12">
         <v>22</v>
       </c>
       <c r="H12">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="J12">
         <v>137</v>
       </c>
       <c r="K12">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13">
@@ -4842,19 +4842,19 @@
         <v>مستجد</v>
       </c>
       <c r="F13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G13">
         <v>22</v>
       </c>
       <c r="H13">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J13">
         <v>158</v>
       </c>
       <c r="K13">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
@@ -4874,19 +4874,19 @@
         <v>مستجد</v>
       </c>
       <c r="F14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G14">
         <v>14</v>
       </c>
       <c r="H14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J14">
         <v>132</v>
       </c>
       <c r="K14">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
@@ -4906,19 +4906,19 @@
         <v>مستجد</v>
       </c>
       <c r="F15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G15">
         <v>24</v>
       </c>
       <c r="H15">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J15">
         <v>177</v>
       </c>
       <c r="K15">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16">
@@ -4938,19 +4938,19 @@
         <v>مستجد</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G16">
         <v>21</v>
       </c>
       <c r="H16">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J16">
         <v>131</v>
       </c>
       <c r="K16">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17">
@@ -4970,19 +4970,19 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G17" t="str">
         <v>غ</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J17">
         <v>68</v>
       </c>
       <c r="K17">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
@@ -5002,19 +5002,19 @@
         <v>مستجد</v>
       </c>
       <c r="F18">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G18">
         <v>21</v>
       </c>
       <c r="H18">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J18">
         <v>136</v>
       </c>
       <c r="K18">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19">
@@ -5034,19 +5034,19 @@
         <v>مستجد</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G19">
         <v>11</v>
       </c>
       <c r="H19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J19">
         <v>105</v>
       </c>
       <c r="K19">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20">
@@ -5066,19 +5066,19 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G20">
         <v>9</v>
       </c>
       <c r="H20">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J20">
         <v>33</v>
       </c>
       <c r="K20">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21">
@@ -5098,19 +5098,19 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G21">
         <v>9</v>
       </c>
       <c r="H21">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J21">
         <v>122</v>
       </c>
       <c r="K21">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22">
@@ -5130,19 +5130,19 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G22">
         <v>12</v>
       </c>
       <c r="H22">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J22">
         <v>121</v>
       </c>
       <c r="K22">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -5162,19 +5162,19 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G23">
         <v>7</v>
       </c>
       <c r="H23">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J23">
         <v>116</v>
       </c>
       <c r="K23">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24">
@@ -5194,19 +5194,19 @@
         <v>مستجد</v>
       </c>
       <c r="F24">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G24">
         <v>20</v>
       </c>
       <c r="H24">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J24">
         <v>153</v>
       </c>
       <c r="K24">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25">
@@ -5226,19 +5226,19 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G25">
         <v>12</v>
       </c>
       <c r="H25">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J25">
         <v>140</v>
       </c>
       <c r="K25">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26">
@@ -5258,19 +5258,19 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G26" t="str">
         <v>غ</v>
       </c>
       <c r="H26">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J26">
         <v>84</v>
       </c>
       <c r="K26">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27">
@@ -5290,19 +5290,19 @@
         <v>مستجد</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G27">
         <v>12</v>
       </c>
       <c r="H27">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J27">
         <v>143</v>
       </c>
       <c r="K27">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28">
@@ -5322,19 +5322,19 @@
         <v>مستجد</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G28">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J28">
         <v>93</v>
       </c>
       <c r="K28">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29">
@@ -5354,19 +5354,19 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G29">
         <v>10</v>
       </c>
       <c r="H29">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J29">
         <v>148</v>
       </c>
       <c r="K29">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30">
@@ -5386,19 +5386,19 @@
         <v>مستجد</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G30">
         <v>10</v>
       </c>
       <c r="H30">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J30">
         <v>81</v>
       </c>
       <c r="K30">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31">
@@ -5537,19 +5537,19 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J3">
         <v>75</v>
       </c>
       <c r="K3">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4">
@@ -5601,19 +5601,19 @@
         <v>مستجد</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G5">
         <v>9</v>
       </c>
       <c r="H5">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J5">
         <v>30</v>
       </c>
       <c r="K5">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -5665,19 +5665,19 @@
         <v>مستجد</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>15</v>
       </c>
       <c r="H7">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J7">
         <v>121</v>
       </c>
       <c r="K7">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8">
@@ -5697,19 +5697,19 @@
         <v>مستجد</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G8">
         <v>17</v>
       </c>
       <c r="H8">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J8">
         <v>139</v>
       </c>
       <c r="K8">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9">
@@ -5761,19 +5761,19 @@
         <v>مستجد</v>
       </c>
       <c r="F10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G10">
         <v>24</v>
       </c>
       <c r="H10">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J10">
         <v>171</v>
       </c>
       <c r="K10">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11">
@@ -5793,19 +5793,19 @@
         <v>مستجد</v>
       </c>
       <c r="F11">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G11">
         <v>11</v>
       </c>
       <c r="H11">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J11">
         <v>128</v>
       </c>
       <c r="K11">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -5825,19 +5825,19 @@
         <v>مستجد</v>
       </c>
       <c r="F12">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G12">
         <v>23</v>
       </c>
       <c r="H12">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J12">
         <v>183</v>
       </c>
       <c r="K12">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13">
@@ -5857,19 +5857,19 @@
         <v>مستجد</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G13">
         <v>14</v>
       </c>
       <c r="H13">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J13">
         <v>93</v>
       </c>
       <c r="K13">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -5889,19 +5889,19 @@
         <v>مستجد</v>
       </c>
       <c r="F14">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G14">
         <v>19</v>
       </c>
       <c r="H14">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J14">
         <v>134</v>
       </c>
       <c r="K14">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15">
@@ -5921,19 +5921,19 @@
         <v>مستجد</v>
       </c>
       <c r="F15">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G15">
         <v>18</v>
       </c>
       <c r="H15">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J15">
         <v>162</v>
       </c>
       <c r="K15">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16">
@@ -5953,19 +5953,19 @@
         <v>مستجد</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G16">
         <v>8</v>
       </c>
       <c r="H16">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J16">
         <v>81</v>
       </c>
       <c r="K16">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17">
@@ -5985,19 +5985,19 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G17">
         <v>20</v>
       </c>
       <c r="H17">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J17">
         <v>181</v>
       </c>
       <c r="K17">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18">
@@ -6049,19 +6049,19 @@
         <v>مستجد</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G19">
         <v>12</v>
       </c>
       <c r="H19">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J19">
         <v>105</v>
       </c>
       <c r="K19">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20">
@@ -6081,19 +6081,19 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G20">
         <v>11</v>
       </c>
       <c r="H20">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J20">
         <v>92</v>
       </c>
       <c r="K20">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21">
@@ -6113,19 +6113,19 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G21">
         <v>23</v>
       </c>
       <c r="H21">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J21">
         <v>149</v>
       </c>
       <c r="K21">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22">
@@ -6145,19 +6145,19 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G22">
         <v>22</v>
       </c>
       <c r="H22">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J22">
         <v>171</v>
       </c>
       <c r="K22">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23">
@@ -6177,19 +6177,19 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G23">
         <v>19</v>
       </c>
       <c r="H23">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="J23">
         <v>135</v>
       </c>
       <c r="K23">
-        <v>167</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24">
@@ -6209,19 +6209,19 @@
         <v>مستجد</v>
       </c>
       <c r="F24">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G24">
         <v>20</v>
       </c>
       <c r="H24">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J24">
         <v>109</v>
       </c>
       <c r="K24">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25">
@@ -6241,19 +6241,19 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G25">
         <v>9</v>
       </c>
       <c r="H25">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J25">
         <v>88</v>
       </c>
       <c r="K25">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26">
@@ -6273,19 +6273,19 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G26">
         <v>11</v>
       </c>
       <c r="H26">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J26">
         <v>123</v>
       </c>
       <c r="K26">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27">
@@ -6305,19 +6305,19 @@
         <v>مستجد</v>
       </c>
       <c r="F27">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G27">
         <v>2</v>
       </c>
       <c r="H27">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J27">
         <v>88</v>
       </c>
       <c r="K27">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28">
@@ -6337,19 +6337,19 @@
         <v>مستجد</v>
       </c>
       <c r="F28">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G28">
         <v>11</v>
       </c>
       <c r="H28">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J28">
         <v>124</v>
       </c>
       <c r="K28">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29">
@@ -6369,19 +6369,19 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G29">
         <v>19</v>
       </c>
       <c r="H29">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="J29">
         <v>146</v>
       </c>
       <c r="K29">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30">
@@ -6401,19 +6401,19 @@
         <v>مستجد</v>
       </c>
       <c r="F30">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G30">
         <v>19</v>
       </c>
       <c r="H30">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J30">
         <v>117</v>
       </c>
       <c r="K30">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31">
@@ -6433,19 +6433,19 @@
         <v>مستجد</v>
       </c>
       <c r="F31">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G31">
         <v>17</v>
       </c>
       <c r="H31">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J31">
         <v>162</v>
       </c>
       <c r="K31">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -6517,19 +6517,19 @@
         <v>مستجد</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J2">
         <v>5</v>
       </c>
       <c r="K2">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -6549,19 +6549,19 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G3">
         <v>13</v>
       </c>
       <c r="H3">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J3">
         <v>123</v>
       </c>
       <c r="K3">
-        <v>149</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4">
@@ -6581,19 +6581,19 @@
         <v>مستجد</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4">
         <v>22</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J4">
         <v>184</v>
       </c>
       <c r="K4">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5">
@@ -6645,19 +6645,19 @@
         <v>مستجد</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <v>7</v>
       </c>
       <c r="H6">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J6">
         <v>131</v>
       </c>
       <c r="K6">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
@@ -6677,19 +6677,19 @@
         <v>مستجد</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G7">
         <v>17</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J7">
         <v>110</v>
       </c>
       <c r="K7">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8">
@@ -6709,19 +6709,19 @@
         <v>مستجد</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G8">
         <v>21</v>
       </c>
       <c r="H8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J8">
         <v>173</v>
       </c>
       <c r="K8">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9">
@@ -6741,19 +6741,19 @@
         <v>مستجد</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G9">
         <v>13</v>
       </c>
       <c r="H9">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J9">
         <v>133</v>
       </c>
       <c r="K9">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
@@ -6773,19 +6773,19 @@
         <v>مستجد</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G10">
         <v>18</v>
       </c>
       <c r="H10">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J10">
         <v>116</v>
       </c>
       <c r="K10">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -6805,19 +6805,19 @@
         <v>مستجد</v>
       </c>
       <c r="F11">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G11">
         <v>20</v>
       </c>
       <c r="H11">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J11">
         <v>127</v>
       </c>
       <c r="K11">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -6837,19 +6837,19 @@
         <v>مستجد</v>
       </c>
       <c r="F12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12">
         <v>19</v>
       </c>
       <c r="H12">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J12">
         <v>144</v>
       </c>
       <c r="K12">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13">
@@ -6869,19 +6869,19 @@
         <v>مستجد</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G13">
         <v>3</v>
       </c>
       <c r="H13">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J13">
         <v>67</v>
       </c>
       <c r="K13">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
@@ -6901,19 +6901,19 @@
         <v>مستجد</v>
       </c>
       <c r="F14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G14">
         <v>20</v>
       </c>
       <c r="H14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J14">
         <v>132</v>
       </c>
       <c r="K14">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15">
@@ -6933,19 +6933,19 @@
         <v>مستجد</v>
       </c>
       <c r="F15">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G15">
         <v>13</v>
       </c>
       <c r="H15">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J15">
         <v>124</v>
       </c>
       <c r="K15">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16">
@@ -6997,19 +6997,19 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G17">
         <v>20</v>
       </c>
       <c r="H17">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J17">
         <v>117</v>
       </c>
       <c r="K17">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18">
@@ -7029,19 +7029,19 @@
         <v>مستجد</v>
       </c>
       <c r="F18">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J18">
         <v>80</v>
       </c>
       <c r="K18">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19">
@@ -7061,19 +7061,19 @@
         <v>مستجد</v>
       </c>
       <c r="F19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19">
         <v>24</v>
       </c>
       <c r="H19">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J19">
         <v>176</v>
       </c>
       <c r="K19">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20">
@@ -7093,19 +7093,19 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G20">
         <v>16</v>
       </c>
       <c r="H20">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J20">
         <v>138</v>
       </c>
       <c r="K20">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21">
@@ -7125,19 +7125,19 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G21">
         <v>16</v>
       </c>
       <c r="H21">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J21">
         <v>88</v>
       </c>
       <c r="K21">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22">
@@ -7157,19 +7157,19 @@
         <v>مستجد بفرصة</v>
       </c>
       <c r="F22">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G22">
         <v>19</v>
       </c>
       <c r="H22">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J22">
         <v>162</v>
       </c>
       <c r="K22">
-        <v>196</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23">
@@ -7201,7 +7201,7 @@
         <v>91</v>
       </c>
       <c r="K23">
-        <v>102</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24">
@@ -7221,19 +7221,19 @@
         <v>باقي</v>
       </c>
       <c r="F24">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G24">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J24">
         <v>123</v>
       </c>
       <c r="K24">
-        <v>149</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25">
@@ -7352,19 +7352,19 @@
         <v>باقي</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G28">
         <v>11</v>
       </c>
       <c r="H28">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J28">
         <v>70</v>
       </c>
       <c r="K28">
-        <v>86</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29">
@@ -7384,19 +7384,19 @@
         <v>باقي</v>
       </c>
       <c r="F29">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G29">
         <v>11</v>
       </c>
       <c r="H29">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J29">
         <v>112</v>
       </c>
       <c r="K29">
-        <v>130</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30">
@@ -7416,19 +7416,19 @@
         <v>باقي</v>
       </c>
       <c r="F30">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G30">
         <v>12</v>
       </c>
       <c r="H30">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J30">
         <v>144</v>
       </c>
       <c r="K30">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31">
@@ -7460,7 +7460,7 @@
         <v>15</v>
       </c>
       <c r="K31">
-        <v>15</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -7544,7 +7544,7 @@
         <v>30</v>
       </c>
       <c r="K2">
-        <v>35</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -7564,19 +7564,19 @@
         <v>باقي</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G3">
         <v>13</v>
       </c>
       <c r="H3">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J3">
         <v>119</v>
       </c>
       <c r="K3">
-        <v>138</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4">
@@ -7628,19 +7628,19 @@
         <v>باقي</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>17</v>
       </c>
       <c r="H5">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J5">
         <v>130</v>
       </c>
       <c r="K5">
-        <v>152</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6">
@@ -7704,7 +7704,7 @@
         <v>79</v>
       </c>
       <c r="K7">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
@@ -7736,7 +7736,7 @@
         <v>54</v>
       </c>
       <c r="K8">
-        <v>66</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -7800,7 +7800,7 @@
         <v>42</v>
       </c>
       <c r="K10">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">
@@ -7963,7 +7963,7 @@
         <v>86</v>
       </c>
       <c r="K15">
-        <v>97</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16">
@@ -7983,19 +7983,19 @@
         <v>باقي</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G16">
         <v>4</v>
       </c>
       <c r="H16">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J16">
         <v>71</v>
       </c>
       <c r="K16">
-        <v>80</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17">
@@ -8059,7 +8059,7 @@
         <v>78</v>
       </c>
       <c r="K18">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
@@ -8143,19 +8143,19 @@
         <v>باقي</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G21">
         <v>12</v>
       </c>
       <c r="H21">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J21">
         <v>104</v>
       </c>
       <c r="K21">
-        <v>125</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22">
@@ -8175,19 +8175,19 @@
         <v>مستجد بفرصة</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G22">
         <v>4</v>
       </c>
       <c r="H22">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J22">
         <v>68</v>
       </c>
       <c r="K22">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23">
@@ -8207,19 +8207,19 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J23">
         <v>42</v>
       </c>
       <c r="K23">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
@@ -8239,19 +8239,19 @@
         <v>مستجد</v>
       </c>
       <c r="F24">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G24">
         <v>24</v>
       </c>
       <c r="H24">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J24">
         <v>170</v>
       </c>
       <c r="K24">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25">
@@ -8271,19 +8271,19 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G25">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J25">
         <v>117</v>
       </c>
       <c r="K25">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
